--- a/data/trans_orig/ESTUDIOS-Clase-trans_orig.xlsx
+++ b/data/trans_orig/ESTUDIOS-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2007</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>282914</t>
+          <t>282293</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>326035</t>
+          <t>324090</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>230826</t>
+          <t>231109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>258344</t>
+          <t>257603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>522103</t>
+          <t>521999</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>576900</t>
+          <t>574299</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94059</t>
+          <t>92890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131522</t>
+          <t>131717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32960</t>
+          <t>33786</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57061</t>
+          <t>57101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>133621</t>
+          <t>131621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>180825</t>
+          <t>178650</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44969</t>
+          <t>46460</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75289</t>
+          <t>74765</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27470</t>
+          <t>26062</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61394</t>
+          <t>62714</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>94547</t>
+          <t>96470</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84768</t>
+          <t>85512</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121972</t>
+          <t>121807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>87995</t>
+          <t>88894</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>123213</t>
+          <t>125148</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184018</t>
+          <t>179084</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>232788</t>
+          <t>231383</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>202725</t>
+          <t>203732</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>243558</t>
+          <t>240767</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>228640</t>
+          <t>227293</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>264825</t>
+          <t>264728</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>444078</t>
+          <t>444329</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>495542</t>
+          <t>498124</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30896</t>
+          <t>29787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54586</t>
+          <t>53830</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12412</t>
+          <t>12263</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32207</t>
+          <t>31794</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46751</t>
+          <t>47390</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77374</t>
+          <t>77505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38337</t>
+          <t>37570</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68799</t>
+          <t>66274</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>46282</t>
+          <t>46224</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77378</t>
+          <t>76446</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>316630</t>
+          <t>314013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>365940</t>
+          <t>360580</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99427</t>
+          <t>97927</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123030</t>
+          <t>123015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>424045</t>
+          <t>426045</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>478780</t>
+          <t>476806</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,14%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>128822</t>
+          <t>132801</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172582</t>
+          <t>173203</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35394</t>
+          <t>36380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58862</t>
+          <t>58990</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>174781</t>
+          <t>173763</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>224426</t>
+          <t>222339</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,31%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35960</t>
+          <t>36097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63058</t>
+          <t>62665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36345</t>
+          <t>35036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65306</t>
+          <t>63354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76738</t>
+          <t>76870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>117330</t>
+          <t>117815</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>584233</t>
+          <t>585967</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>655025</t>
+          <t>651926</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>392503</t>
+          <t>393162</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>444637</t>
+          <t>446816</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>994901</t>
+          <t>994366</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1084265</t>
+          <t>1085305</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,58%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>536072</t>
+          <t>538133</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>603601</t>
+          <t>604781</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>222207</t>
+          <t>223310</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>271905</t>
+          <t>274740</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>769203</t>
+          <t>774342</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>861972</t>
+          <t>864002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19908</t>
+          <t>19627</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>11195</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>30150</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>152977</t>
+          <t>151930</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>189960</t>
+          <t>190529</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>245076</t>
+          <t>247108</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>296151</t>
+          <t>295797</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>410938</t>
+          <t>411829</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>475133</t>
+          <t>472979</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,45%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149475</t>
+          <t>148979</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>187251</t>
+          <t>187966</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>265321</t>
+          <t>265495</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>314362</t>
+          <t>313819</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>428422</t>
+          <t>426945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>491911</t>
+          <t>488397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,13%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24021</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46202</t>
+          <t>46125</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46830</t>
+          <t>46079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>78569</t>
+          <t>78179</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>77616</t>
+          <t>75930</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>115309</t>
+          <t>115462</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>210131</t>
+          <t>208680</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>239552</t>
+          <t>238957</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>458589</t>
+          <t>461663</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>530623</t>
+          <t>530074</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>681427</t>
+          <t>677020</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>756747</t>
+          <t>758407</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,03%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29026</t>
+          <t>29217</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>52639</t>
+          <t>52341</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>658253</t>
+          <t>656587</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>727671</t>
+          <t>722796</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>692504</t>
+          <t>694075</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>768485</t>
+          <t>772108</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>504318</t>
+          <t>504693</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>587990</t>
+          <t>596061</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>436145</t>
+          <t>436893</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>520419</t>
+          <t>517608</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>971349</t>
+          <t>967317</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1091762</t>
+          <t>1091541</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1632250</t>
+          <t>1635058</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1746740</t>
+          <t>1747324</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1533164</t>
+          <t>1530699</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1648901</t>
+          <t>1647473</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3197144</t>
+          <t>3197681</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3371231</t>
+          <t>3365281</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>973125</t>
+          <t>981401</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1082233</t>
+          <t>1081001</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1257282</t>
+          <t>1260115</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1367259</t>
+          <t>1370840</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2264941</t>
+          <t>2262748</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2420528</t>
+          <t>2415757</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2012</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>223383</t>
+          <t>223767</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>266957</t>
+          <t>268147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>213456</t>
+          <t>211572</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>246489</t>
+          <t>246288</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>448077</t>
+          <t>451323</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>505895</t>
+          <t>505489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,25%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>128739</t>
+          <t>129002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>171915</t>
+          <t>172235</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55390</t>
+          <t>56115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86625</t>
+          <t>87809</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>193767</t>
+          <t>193145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247230</t>
+          <t>245427</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30995</t>
+          <t>30492</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56549</t>
+          <t>56067</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>22117</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41105</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73098</t>
+          <t>72633</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>97044</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>138062</t>
+          <t>136513</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75784</t>
+          <t>76351</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112443</t>
+          <t>111846</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183076</t>
+          <t>183514</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>236275</t>
+          <t>239459</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>250398</t>
+          <t>249367</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>292737</t>
+          <t>292246</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>197240</t>
+          <t>196208</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>234764</t>
+          <t>233901</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>458181</t>
+          <t>457700</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>515114</t>
+          <t>516322</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,48%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18831</t>
+          <t>18542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40656</t>
+          <t>40593</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19593</t>
+          <t>19960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39956</t>
+          <t>41870</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43275</t>
+          <t>43206</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72771</t>
+          <t>72808</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22961</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47206</t>
+          <t>47240</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16114</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30691</t>
+          <t>30232</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58536</t>
+          <t>58886</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>359405</t>
+          <t>362045</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>409351</t>
+          <t>410048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>132407</t>
+          <t>131727</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165158</t>
+          <t>164106</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>505545</t>
+          <t>507293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>566974</t>
+          <t>566867</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,82%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183156</t>
+          <t>185112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>232176</t>
+          <t>231707</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87578</t>
+          <t>88820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>120100</t>
+          <t>120915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280846</t>
+          <t>282682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340039</t>
+          <t>339615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31755</t>
+          <t>32760</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62824</t>
+          <t>63227</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34253</t>
+          <t>34157</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63728</t>
+          <t>63084</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70725</t>
+          <t>72336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111636</t>
+          <t>113357</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>654495</t>
+          <t>649335</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>723057</t>
+          <t>722951</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>513454</t>
+          <t>514095</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>568800</t>
+          <t>565866</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1188518</t>
+          <t>1188525</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1274162</t>
+          <t>1272902</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,27%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>387059</t>
+          <t>388876</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>454069</t>
+          <t>460473</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>151699</t>
+          <t>153043</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>201683</t>
+          <t>201243</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>557100</t>
+          <t>558236</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>637326</t>
+          <t>641709</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21604</t>
+          <t>20928</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25115</t>
+          <t>25945</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41849</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>222843</t>
+          <t>222136</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>268200</t>
+          <t>266556</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>306407</t>
+          <t>307449</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>362524</t>
+          <t>362602</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>543037</t>
+          <t>540790</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>620159</t>
+          <t>616043</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,5%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>227098</t>
+          <t>232235</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>273964</t>
+          <t>276023</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>380159</t>
+          <t>381923</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>438121</t>
+          <t>438824</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>624709</t>
+          <t>625473</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>698326</t>
+          <t>700081</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,12%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19377</t>
+          <t>19321</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>38404</t>
+          <t>37641</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49744</t>
+          <t>49572</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>83065</t>
+          <t>80871</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>74736</t>
+          <t>73753</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>112052</t>
+          <t>113143</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>205100</t>
+          <t>204855</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>229701</t>
+          <t>229667</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>407538</t>
+          <t>409961</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>473505</t>
+          <t>475462</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>620757</t>
+          <t>621354</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>697284</t>
+          <t>700179</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13069</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31531</t>
+          <t>32509</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>569492</t>
+          <t>567927</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>636766</t>
+          <t>632643</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>585696</t>
+          <t>586167</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>662117</t>
+          <t>665300</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>438924</t>
+          <t>439551</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>529337</t>
+          <t>526875</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>418547</t>
+          <t>414933</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>500392</t>
+          <t>499355</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>883016</t>
+          <t>879958</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>998052</t>
+          <t>1003725</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1902952</t>
+          <t>1900488</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026483</t>
+          <t>2021753</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1693105</t>
+          <t>1692720</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1817543</t>
+          <t>1815515</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3633587</t>
+          <t>3621335</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3805817</t>
+          <t>3796971</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,55%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>917184</t>
+          <t>919056</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1023818</t>
+          <t>1027404</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1274279</t>
+          <t>1283311</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1393902</t>
+          <t>1393698</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2224527</t>
+          <t>2228812</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2389545</t>
+          <t>2390307</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2016</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>269958</t>
+          <t>273404</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>311080</t>
+          <t>314197</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>254904</t>
+          <t>255453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>287353</t>
+          <t>284672</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>536355</t>
+          <t>538982</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>587402</t>
+          <t>589133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,03%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99743</t>
+          <t>97721</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>136984</t>
+          <t>135604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56019</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86824</t>
+          <t>86068</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>166073</t>
+          <t>166846</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214153</t>
+          <t>214807</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26852</t>
+          <t>25551</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>11411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13180</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31335</t>
+          <t>32219</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98537</t>
+          <t>99518</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>136521</t>
+          <t>136121</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88929</t>
+          <t>87584</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>123144</t>
+          <t>122170</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197577</t>
+          <t>199018</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>247230</t>
+          <t>248778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>217184</t>
+          <t>217163</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>255398</t>
+          <t>255733</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>239652</t>
+          <t>238677</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>273231</t>
+          <t>275284</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>468873</t>
+          <t>468737</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>520154</t>
+          <t>521572</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,98%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>12693</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30570</t>
+          <t>30787</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41261</t>
+          <t>40409</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22082</t>
+          <t>23341</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44221</t>
+          <t>46218</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22604</t>
+          <t>22824</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>33401</t>
+          <t>34790</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60804</t>
+          <t>61090</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>338916</t>
+          <t>338413</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>380059</t>
+          <t>381804</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100994</t>
+          <t>101382</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125604</t>
+          <t>125737</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>449912</t>
+          <t>449584</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>497375</t>
+          <t>496650</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,6%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110431</t>
+          <t>108516</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148843</t>
+          <t>147685</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>25553</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48176</t>
+          <t>48290</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143229</t>
+          <t>144365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>187773</t>
+          <t>186447</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27691</t>
+          <t>28249</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54093</t>
+          <t>53359</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56710</t>
+          <t>56795</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90048</t>
+          <t>89446</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92479</t>
+          <t>93708</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133833</t>
+          <t>135556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>749595</t>
+          <t>756254</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>815233</t>
+          <t>821433</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>583143</t>
+          <t>582249</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>632844</t>
+          <t>632812</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1351302</t>
+          <t>1345412</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1431819</t>
+          <t>1431758</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>291758</t>
+          <t>289041</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>353934</t>
+          <t>348655</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>121909</t>
+          <t>121171</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>164413</t>
+          <t>164139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>427805</t>
+          <t>426448</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>503705</t>
+          <t>500953</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27732</t>
+          <t>27775</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>16609</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37442</t>
+          <t>37790</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32224</t>
+          <t>30667</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59455</t>
+          <t>57979</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>317198</t>
+          <t>319596</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367178</t>
+          <t>367256</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>352300</t>
+          <t>353164</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>409183</t>
+          <t>407769</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>686404</t>
+          <t>689136</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>760264</t>
+          <t>760276</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>232120</t>
+          <t>231652</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>280008</t>
+          <t>277083</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>303377</t>
+          <t>304217</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>359984</t>
+          <t>358759</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>546962</t>
+          <t>552195</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>622050</t>
+          <t>624928</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,2%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34025</t>
+          <t>35042</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58979</t>
+          <t>59969</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46400</t>
+          <t>47465</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>75949</t>
+          <t>77243</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>88156</t>
+          <t>86702</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>125187</t>
+          <t>125867</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>211642</t>
+          <t>211773</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>238975</t>
+          <t>238708</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>517883</t>
+          <t>517258</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>585233</t>
+          <t>583510</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>736725</t>
+          <t>742091</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>818619</t>
+          <t>816029</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21922</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>434610</t>
+          <t>434084</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>502783</t>
+          <t>502874</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>442391</t>
+          <t>442894</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>517965</t>
+          <t>517011</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,91%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>501202</t>
+          <t>502664</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>594256</t>
+          <t>587762</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>502804</t>
+          <t>506348</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>593665</t>
+          <t>594268</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1035806</t>
+          <t>1031201</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1152916</t>
+          <t>1157828</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2011757</t>
+          <t>2018734</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2128665</t>
+          <t>2130340</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1919465</t>
+          <t>1919764</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2041186</t>
+          <t>2038274</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3968691</t>
+          <t>3972143</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4133265</t>
+          <t>4145872</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,19%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>707087</t>
+          <t>705195</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>804956</t>
+          <t>796139</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>931400</t>
+          <t>934753</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1038182</t>
+          <t>1044532</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1668174</t>
+          <t>1661352</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1814123</t>
+          <t>1815361</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2023</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>345687</t>
+          <t>347977</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>389806</t>
+          <t>390032</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>342688</t>
+          <t>344785</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>373261</t>
+          <t>372385</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>701880</t>
+          <t>702413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>753902</t>
+          <t>753325</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,17%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104597</t>
+          <t>104421</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146938</t>
+          <t>145804</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65034</t>
+          <t>66749</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94627</t>
+          <t>94188</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>178829</t>
+          <t>178740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>231032</t>
+          <t>229532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14828</t>
+          <t>16090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>12283</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28282</t>
+          <t>26734</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104600</t>
+          <t>105593</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142999</t>
+          <t>144443</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>129672</t>
+          <t>130380</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>161203</t>
+          <t>161599</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>246887</t>
+          <t>244558</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>298594</t>
+          <t>298275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>288632</t>
+          <t>287680</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>329243</t>
+          <t>328051</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>211623</t>
+          <t>210825</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>242973</t>
+          <t>243176</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>509134</t>
+          <t>509258</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>561155</t>
+          <t>561032</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>11147</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25571</t>
+          <t>25372</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14923</t>
+          <t>15320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18477</t>
+          <t>18966</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36265</t>
+          <t>36065</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52474</t>
+          <t>54757</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>19278</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>15821</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>64333</t>
+          <t>65464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>504890</t>
+          <t>502119</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>631503</t>
+          <t>631873</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106957</t>
+          <t>105007</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124229</t>
+          <t>124858</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>615644</t>
+          <t>616470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>771529</t>
+          <t>768938</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25774</t>
+          <t>25805</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115109</t>
+          <t>118019</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>30769</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47391</t>
+          <t>47592</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45186</t>
+          <t>46574</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>160196</t>
+          <t>158193</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42205</t>
+          <t>41767</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91308</t>
+          <t>92240</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31815</t>
+          <t>27876</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83673</t>
+          <t>85681</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83697</t>
+          <t>84462</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>151262</t>
+          <t>150643</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>697378</t>
+          <t>696437</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>758851</t>
+          <t>761808</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>759360</t>
+          <t>759091</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>881365</t>
+          <t>898648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1479890</t>
+          <t>1471676</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1690660</t>
+          <t>1691890</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>217436</t>
+          <t>217363</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>271094</t>
+          <t>271783</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>59140</t>
+          <t>49343</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>137794</t>
+          <t>138951</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>238800</t>
+          <t>240832</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>396710</t>
+          <t>401650</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20757</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10777</t>
+          <t>11403</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26270</t>
+          <t>26849</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43169</t>
+          <t>41797</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>277524</t>
+          <t>276345</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>320633</t>
+          <t>321096</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>501754</t>
+          <t>498350</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>626681</t>
+          <t>613454</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>797379</t>
+          <t>797099</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>927855</t>
+          <t>924361</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>142224</t>
+          <t>143636</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>183984</t>
+          <t>185649</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>200332</t>
+          <t>213722</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>319490</t>
+          <t>322780</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>369716</t>
+          <t>365745</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>484989</t>
+          <t>486907</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16388</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46104</t>
+          <t>47050</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30259</t>
+          <t>29523</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>57177</t>
+          <t>54779</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51337</t>
+          <t>51868</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>90826</t>
+          <t>91195</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>188445</t>
+          <t>187369</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>219916</t>
+          <t>219413</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>384624</t>
+          <t>385502</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>436191</t>
+          <t>435804</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>585138</t>
+          <t>583222</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>650972</t>
+          <t>648740</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,0%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13468</t>
+          <t>13636</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>280028</t>
+          <t>281355</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>328225</t>
+          <t>329373</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>282627</t>
+          <t>282430</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>338718</t>
+          <t>339566</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>485332</t>
+          <t>494429</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>691558</t>
+          <t>684408</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>527603</t>
+          <t>502930</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>701463</t>
+          <t>699603</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1078323</t>
+          <t>1093079</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1360288</t>
+          <t>1367594</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2131395</t>
+          <t>2137174</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2470111</t>
+          <t>2481254</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2077318</t>
+          <t>2068986</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2473011</t>
+          <t>2478559</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4258193</t>
+          <t>4239660</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4766356</t>
+          <t>4776886</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>404052</t>
+          <t>406850</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>564586</t>
+          <t>564707</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>596224</t>
+          <t>595196</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>812314</t>
+          <t>814836</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1097647</t>
+          <t>1081173</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1355251</t>
+          <t>1353224</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ESTUDIOS-Clase-trans_orig.xlsx
+++ b/data/trans_orig/ESTUDIOS-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>282293</t>
+          <t>279096</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>324090</t>
+          <t>322243</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>231109</t>
+          <t>230853</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>257603</t>
+          <t>258554</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>521999</t>
+          <t>522389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>574299</t>
+          <t>573271</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92890</t>
+          <t>93645</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131717</t>
+          <t>129551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33786</t>
+          <t>32267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57101</t>
+          <t>57732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>131621</t>
+          <t>133824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>178650</t>
+          <t>179791</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46460</t>
+          <t>47241</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74765</t>
+          <t>76162</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>9830</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26062</t>
+          <t>26840</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62714</t>
+          <t>61564</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96470</t>
+          <t>95585</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85512</t>
+          <t>87896</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121807</t>
+          <t>123199</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88894</t>
+          <t>88156</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>125148</t>
+          <t>122272</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>179084</t>
+          <t>184238</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>231383</t>
+          <t>235486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>203732</t>
+          <t>201696</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>240767</t>
+          <t>240922</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>227293</t>
+          <t>229026</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>264728</t>
+          <t>266050</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>444329</t>
+          <t>441219</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>498124</t>
+          <t>495291</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29787</t>
+          <t>29808</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53830</t>
+          <t>54617</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12263</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31794</t>
+          <t>30230</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47390</t>
+          <t>47291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77505</t>
+          <t>77898</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37570</t>
+          <t>37170</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>66274</t>
+          <t>66859</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>17642</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>46224</t>
+          <t>46958</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>76446</t>
+          <t>79041</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>314013</t>
+          <t>316857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>360580</t>
+          <t>363681</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97927</t>
+          <t>98494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123015</t>
+          <t>122193</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>426045</t>
+          <t>427074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>476806</t>
+          <t>475900</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,01%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132801</t>
+          <t>130971</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173203</t>
+          <t>172655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36380</t>
+          <t>35818</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58990</t>
+          <t>59328</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173763</t>
+          <t>174162</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>222339</t>
+          <t>222267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36097</t>
+          <t>35480</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62665</t>
+          <t>63551</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35036</t>
+          <t>35498</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63354</t>
+          <t>63588</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,47 +2151,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>8,9%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>95688</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>77616</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>116238</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>4,9%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>8,87%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>95688</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>76870</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>117815</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>585967</t>
+          <t>581981</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>651926</t>
+          <t>652666</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>393162</t>
+          <t>394090</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>446816</t>
+          <t>446622</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>994366</t>
+          <t>997485</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1085305</t>
+          <t>1085935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>538133</t>
+          <t>537717</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>604781</t>
+          <t>607546</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>223310</t>
+          <t>221677</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>274740</t>
+          <t>274387</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>774342</t>
+          <t>770477</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>864002</t>
+          <t>858117</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19627</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11195</t>
+          <t>10885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30150</t>
+          <t>29262</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>151930</t>
+          <t>151851</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>190529</t>
+          <t>191561</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>247108</t>
+          <t>245382</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>295797</t>
+          <t>294551</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>411829</t>
+          <t>410081</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>472979</t>
+          <t>474768</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,64%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148979</t>
+          <t>147929</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>187966</t>
+          <t>187755</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>265495</t>
+          <t>267340</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>313819</t>
+          <t>316069</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>426945</t>
+          <t>428397</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>488397</t>
+          <t>492438</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,57%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24430</t>
+          <t>23238</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46125</t>
+          <t>45517</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46079</t>
+          <t>48069</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>78179</t>
+          <t>79534</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>75930</t>
+          <t>76901</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>115462</t>
+          <t>114590</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>208680</t>
+          <t>209265</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>238957</t>
+          <t>238354</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>461663</t>
+          <t>460382</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>530074</t>
+          <t>528493</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>677020</t>
+          <t>682953</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>758407</t>
+          <t>758661</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,04%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29217</t>
+          <t>28813</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>52341</t>
+          <t>52940</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>656587</t>
+          <t>658571</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>722796</t>
+          <t>730136</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>694075</t>
+          <t>690197</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>772108</t>
+          <t>768171</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,66%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>504693</t>
+          <t>507279</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>596061</t>
+          <t>591375</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,82 +3484,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>15,51%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>18,08%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>476412</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>436553</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>516238</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>14,1%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>12,92%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>15,28%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>1025847</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>968523</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>1084808</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>15,43%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>476412</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>436893</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>517608</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>14,1%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>12,93%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>15,32%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>1025847</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>967317</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>1091541</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>15,43%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1635058</t>
+          <t>1636529</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1747324</t>
+          <t>1753368</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1530699</t>
+          <t>1537151</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1647473</t>
+          <t>1651319</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3197681</t>
+          <t>3195347</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3365281</t>
+          <t>3358893</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,52%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>981401</t>
+          <t>976200</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1081001</t>
+          <t>1080440</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1260115</t>
+          <t>1257173</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1370840</t>
+          <t>1369107</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2262748</t>
+          <t>2265746</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2415757</t>
+          <t>2424124</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>223767</t>
+          <t>222303</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>268147</t>
+          <t>266647</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>211572</t>
+          <t>213840</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>246288</t>
+          <t>245968</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>451323</t>
+          <t>449678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>505489</t>
+          <t>503200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,94%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129002</t>
+          <t>130920</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172235</t>
+          <t>172373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56115</t>
+          <t>54829</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87809</t>
+          <t>87081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>193145</t>
+          <t>195968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>245427</t>
+          <t>246085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30492</t>
+          <t>29390</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56067</t>
+          <t>56088</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22117</t>
+          <t>22448</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>40964</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72633</t>
+          <t>70982</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97044</t>
+          <t>95810</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>136513</t>
+          <t>137682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76351</t>
+          <t>76065</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111846</t>
+          <t>110218</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183514</t>
+          <t>182914</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>239459</t>
+          <t>236363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>249367</t>
+          <t>251410</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>292246</t>
+          <t>293265</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>196208</t>
+          <t>196884</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>233901</t>
+          <t>233381</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>457700</t>
+          <t>460071</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>516322</t>
+          <t>517585</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,65%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18542</t>
+          <t>18848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40593</t>
+          <t>40352</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19960</t>
+          <t>19863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41870</t>
+          <t>40550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43206</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72808</t>
+          <t>72973</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23225</t>
+          <t>24014</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47240</t>
+          <t>50613</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16290</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30232</t>
+          <t>30337</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58886</t>
+          <t>57436</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>362045</t>
+          <t>360862</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>410048</t>
+          <t>413032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131727</t>
+          <t>132573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164106</t>
+          <t>164511</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>507293</t>
+          <t>506124</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>566867</t>
+          <t>565371</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,65%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>185112</t>
+          <t>183437</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>231707</t>
+          <t>232934</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88820</t>
+          <t>87560</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>120915</t>
+          <t>120044</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>282682</t>
+          <t>280479</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>339615</t>
+          <t>340700</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32760</t>
+          <t>31431</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63227</t>
+          <t>60628</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34157</t>
+          <t>35259</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63084</t>
+          <t>62311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72336</t>
+          <t>71801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113357</t>
+          <t>112944</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>649335</t>
+          <t>656996</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>722951</t>
+          <t>725685</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>514095</t>
+          <t>516190</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>565866</t>
+          <t>567175</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1188525</t>
+          <t>1186963</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1272902</t>
+          <t>1274868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,37%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>388876</t>
+          <t>384969</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>460473</t>
+          <t>454429</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>153043</t>
+          <t>153022</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>201243</t>
+          <t>199459</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>558236</t>
+          <t>557293</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>641709</t>
+          <t>639937</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20928</t>
+          <t>21129</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>25260</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>18085</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40739</t>
+          <t>41542</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>222136</t>
+          <t>221577</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>266556</t>
+          <t>268086</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>307449</t>
+          <t>306341</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>362602</t>
+          <t>364003</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>540790</t>
+          <t>547686</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>616043</t>
+          <t>618163</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>232235</t>
+          <t>231247</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>276023</t>
+          <t>275542</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>381923</t>
+          <t>379501</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>438824</t>
+          <t>438436</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>625473</t>
+          <t>624268</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>700081</t>
+          <t>694304</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>54,66%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19321</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>37641</t>
+          <t>38690</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49572</t>
+          <t>49149</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80871</t>
+          <t>80385</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73753</t>
+          <t>73459</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>113143</t>
+          <t>112033</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>204855</t>
+          <t>205539</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>229667</t>
+          <t>230402</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>409961</t>
+          <t>409378</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>475462</t>
+          <t>477133</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>621354</t>
+          <t>623200</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>700179</t>
+          <t>699558</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>12880</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32509</t>
+          <t>31602</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>567927</t>
+          <t>564925</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>632643</t>
+          <t>634467</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>586167</t>
+          <t>585060</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>665300</t>
+          <t>662116</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,11%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>439551</t>
+          <t>441347</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>526875</t>
+          <t>531135</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>414933</t>
+          <t>417051</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>499355</t>
+          <t>504190</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>879958</t>
+          <t>881487</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1003725</t>
+          <t>998357</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1900488</t>
+          <t>1899787</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2021753</t>
+          <t>2022184</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1692720</t>
+          <t>1687185</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1815515</t>
+          <t>1813027</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3621335</t>
+          <t>3626488</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3796971</t>
+          <t>3795348</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>919056</t>
+          <t>921191</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1027404</t>
+          <t>1029465</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1283311</t>
+          <t>1273944</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1393698</t>
+          <t>1394196</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2228812</t>
+          <t>2232287</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2390307</t>
+          <t>2387634</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>273404</t>
+          <t>270716</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>314197</t>
+          <t>312925</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>255453</t>
+          <t>254677</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>284672</t>
+          <t>285201</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>538982</t>
+          <t>541844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>589133</t>
+          <t>590232</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,17%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97721</t>
+          <t>96960</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135604</t>
+          <t>138008</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58000</t>
+          <t>57002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86068</t>
+          <t>87855</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>166846</t>
+          <t>165094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214807</t>
+          <t>211213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25551</t>
+          <t>27020</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>10484</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13414</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32219</t>
+          <t>33064</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99518</t>
+          <t>99015</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>136121</t>
+          <t>134863</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>87584</t>
+          <t>90278</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>122170</t>
+          <t>124529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>199018</t>
+          <t>196472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>248778</t>
+          <t>249549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>217163</t>
+          <t>218735</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>255733</t>
+          <t>255924</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>238677</t>
+          <t>236953</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>275284</t>
+          <t>273039</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>468737</t>
+          <t>465712</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>521572</t>
+          <t>521376</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,95%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>12386</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16812</t>
+          <t>16821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18157</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40409</t>
+          <t>39654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23341</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46218</t>
+          <t>44111</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7534</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22824</t>
+          <t>23053</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34790</t>
+          <t>34821</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61090</t>
+          <t>60303</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>338413</t>
+          <t>339954</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>381804</t>
+          <t>380951</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101382</t>
+          <t>100750</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125737</t>
+          <t>124919</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>449584</t>
+          <t>449348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>496650</t>
+          <t>497596</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,73%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108516</t>
+          <t>109227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147685</t>
+          <t>148000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25553</t>
+          <t>25850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48290</t>
+          <t>48417</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144365</t>
+          <t>141437</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>186447</t>
+          <t>187822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28249</t>
+          <t>28046</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53359</t>
+          <t>54674</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56795</t>
+          <t>57095</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89446</t>
+          <t>91256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>92018</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135556</t>
+          <t>137818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>756254</t>
+          <t>752260</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>821433</t>
+          <t>815753</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>582249</t>
+          <t>582978</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>632812</t>
+          <t>630180</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1345412</t>
+          <t>1354350</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1431758</t>
+          <t>1434933</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,94%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>289041</t>
+          <t>292629</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>348655</t>
+          <t>356241</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>121171</t>
+          <t>120348</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>164139</t>
+          <t>163751</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>426448</t>
+          <t>426751</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>500953</t>
+          <t>499259</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27775</t>
+          <t>28085</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16609</t>
+          <t>17141</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37790</t>
+          <t>38325</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30667</t>
+          <t>30548</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57979</t>
+          <t>58902</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>319596</t>
+          <t>318504</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367256</t>
+          <t>368625</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>353164</t>
+          <t>352698</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>407769</t>
+          <t>410035</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>689136</t>
+          <t>689268</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>760276</t>
+          <t>762482</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>231652</t>
+          <t>230681</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>277083</t>
+          <t>280478</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>304217</t>
+          <t>299960</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>358759</t>
+          <t>358122</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>552195</t>
+          <t>545724</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>624928</t>
+          <t>620363</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,86%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35042</t>
+          <t>33286</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59969</t>
+          <t>58948</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47465</t>
+          <t>46837</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>77243</t>
+          <t>77749</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>86702</t>
+          <t>87409</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>125867</t>
+          <t>125366</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>211773</t>
+          <t>213102</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>238708</t>
+          <t>240481</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>517258</t>
+          <t>515631</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>583510</t>
+          <t>581238</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>742091</t>
+          <t>737310</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>816029</t>
+          <t>815002</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20732</t>
+          <t>20812</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>434084</t>
+          <t>434769</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>502874</t>
+          <t>500283</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>442894</t>
+          <t>444452</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>517011</t>
+          <t>518084</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>502664</t>
+          <t>500071</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>587762</t>
+          <t>591245</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>506348</t>
+          <t>506373</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>594268</t>
+          <t>595818</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1031201</t>
+          <t>1031301</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1157828</t>
+          <t>1156202</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2018734</t>
+          <t>2016346</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2130340</t>
+          <t>2124953</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1919764</t>
+          <t>1922743</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2038274</t>
+          <t>2037414</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3972143</t>
+          <t>3979654</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4145872</t>
+          <t>4146643</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,2%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>705195</t>
+          <t>709667</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>796139</t>
+          <t>803020</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>934753</t>
+          <t>931758</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1044532</t>
+          <t>1043585</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1661352</t>
+          <t>1665215</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1815361</t>
+          <t>1809308</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>370029</t>
+          <t>403419</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>347977</t>
+          <t>380958</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>390032</t>
+          <t>424624</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>358948</t>
+          <t>386062</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>344785</t>
+          <t>368388</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>372385</t>
+          <t>402259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>728977</t>
+          <t>789480</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>702413</t>
+          <t>760896</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>753325</t>
+          <t>814014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,43%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>123856</t>
+          <t>134330</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104421</t>
+          <t>113343</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145804</t>
+          <t>155803</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79499</t>
+          <t>92448</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66749</t>
+          <t>77436</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94188</t>
+          <t>109348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>203355</t>
+          <t>226778</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>178740</t>
+          <t>201847</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>229532</t>
+          <t>254196</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -11232,22 +11232,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16090</t>
+          <t>16150</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>19139</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>14453</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26734</t>
+          <t>30911</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>504004</t>
+          <t>549422</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>504004</t>
+          <t>549422</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>504004</t>
+          <t>549422</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>951471</t>
+          <t>1037832</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>951471</t>
+          <t>1037832</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>951471</t>
+          <t>1037832</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>124849</t>
+          <t>133446</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>105593</t>
+          <t>112545</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>144443</t>
+          <t>152745</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>145555</t>
+          <t>159600</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>130380</t>
+          <t>143579</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>161599</t>
+          <t>176725</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>270403</t>
+          <t>293045</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>244558</t>
+          <t>265083</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>298275</t>
+          <t>319936</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>308865</t>
+          <t>329968</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>287680</t>
+          <t>310290</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>328051</t>
+          <t>352315</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>227467</t>
+          <t>253282</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>210825</t>
+          <t>237287</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>243176</t>
+          <t>270351</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>536333</t>
+          <t>583250</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>509258</t>
+          <t>557020</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>561032</t>
+          <t>611563</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,63%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11147</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>26347</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15320</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>26641</t>
+          <t>27943</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>20462</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36065</t>
+          <t>39041</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>450797</t>
+          <t>481095</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>450797</t>
+          <t>481095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>450797</t>
+          <t>481095</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>833377</t>
+          <t>904238</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>833377</t>
+          <t>904238</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>833377</t>
+          <t>904238</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28970</t>
+          <t>34934</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>23893</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54757</t>
+          <t>51694</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>15573</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>10155</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>23251</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>41090</t>
+          <t>50507</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>36889</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65464</t>
+          <t>67870</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>570172</t>
+          <t>359856</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>502119</t>
+          <t>338287</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>631873</t>
+          <t>375541</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>115742</t>
+          <t>129932</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105007</t>
+          <t>119565</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124858</t>
+          <t>140384</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>685914</t>
+          <t>489788</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>616470</t>
+          <t>467383</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>768938</t>
+          <t>509404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>77,29%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>69122</t>
+          <t>76822</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25805</t>
+          <t>62999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118019</t>
+          <t>93250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>39049</t>
+          <t>41992</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30769</t>
+          <t>32809</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47592</t>
+          <t>50892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>108171</t>
+          <t>118814</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46574</t>
+          <t>101030</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>158193</t>
+          <t>137550</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>57960</t>
+          <t>65028</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41767</t>
+          <t>48854</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92240</t>
+          <t>87041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>61621</t>
+          <t>75023</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>61896</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85681</t>
+          <t>90636</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>119580</t>
+          <t>140051</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84462</t>
+          <t>118336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150643</t>
+          <t>168179</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>5,95%</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>730686</t>
+          <t>798827</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>696437</t>
+          <t>765296</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>761808</t>
+          <t>827581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>810722</t>
+          <t>665702</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>759091</t>
+          <t>647184</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>898648</t>
+          <t>686424</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1541408</t>
+          <t>1464529</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1471676</t>
+          <t>1425905</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1691890</t>
+          <t>1499983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>75,43%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>244122</t>
+          <t>264709</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>217363</t>
+          <t>236030</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>271783</t>
+          <t>292798</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>104999</t>
+          <t>119265</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49343</t>
+          <t>102602</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>138951</t>
+          <t>135673</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>349122</t>
+          <t>383974</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>240832</t>
+          <t>355313</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>401650</t>
+          <t>412433</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1032768</t>
+          <t>1128564</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1032768</t>
+          <t>1128564</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1032768</t>
+          <t>1128564</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>977342</t>
+          <t>859990</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>977342</t>
+          <t>859990</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>977342</t>
+          <t>859990</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2010110</t>
+          <t>1988554</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2010110</t>
+          <t>1988554</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2010110</t>
+          <t>1988554</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>14353</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>23344</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18036</t>
+          <t>24180</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26849</t>
+          <t>34739</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>29518</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20868</t>
+          <t>28757</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41797</t>
+          <t>54380</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>299778</t>
+          <t>355946</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>276345</t>
+          <t>330566</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>321096</t>
+          <t>379668</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>544183</t>
+          <t>504918</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>498350</t>
+          <t>482378</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>613454</t>
+          <t>530020</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>843962</t>
+          <t>860865</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>797099</t>
+          <t>823807</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>924361</t>
+          <t>892418</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>162632</t>
+          <t>195359</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>143636</t>
+          <t>173401</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>185649</t>
+          <t>220860</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>278521</t>
+          <t>301090</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>213722</t>
+          <t>277902</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>322780</t>
+          <t>321728</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>441153</t>
+          <t>496449</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>365745</t>
+          <t>466431</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>486907</t>
+          <t>532500</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>473893</t>
+          <t>565658</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>473893</t>
+          <t>565658</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>473893</t>
+          <t>565658</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>840740</t>
+          <t>830188</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>840740</t>
+          <t>830188</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>840740</t>
+          <t>830188</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1314633</t>
+          <t>1395846</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1314633</t>
+          <t>1395846</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1314633</t>
+          <t>1395846</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,32 +13286,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27552</t>
+          <t>31158</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>19039</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47050</t>
+          <t>49011</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>41353</t>
+          <t>47226</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29523</t>
+          <t>34575</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54779</t>
+          <t>64747</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>68906</t>
+          <t>78383</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51868</t>
+          <t>59814</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>91195</t>
+          <t>100650</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -13399,32 +13399,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>206955</t>
+          <t>200121</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>187369</t>
+          <t>181339</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>219413</t>
+          <t>213201</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>411756</t>
+          <t>466540</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>385502</t>
+          <t>438970</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>435804</t>
+          <t>494584</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>618712</t>
+          <t>666661</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>583222</t>
+          <t>632809</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>648740</t>
+          <t>700760</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,9%</t>
         </is>
       </c>
     </row>
@@ -13512,32 +13512,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13636</t>
+          <t>14859</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>304440</t>
+          <t>328801</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>281355</t>
+          <t>304044</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>329373</t>
+          <t>353799</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>310440</t>
+          <t>334750</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>282430</t>
+          <t>306620</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>339566</t>
+          <t>367227</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>757549</t>
+          <t>842566</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>757549</t>
+          <t>842566</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>757549</t>
+          <t>842566</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>998057</t>
+          <t>1079794</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>998057</t>
+          <t>1079794</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>998057</t>
+          <t>1079794</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>620842</t>
+          <t>682336</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>494429</t>
+          <t>629997</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>684408</t>
+          <t>735606</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>637633</t>
+          <t>707663</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>502930</t>
+          <t>664534</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>699603</t>
+          <t>750462</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1258475</t>
+          <t>1389999</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1093079</t>
+          <t>1324346</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1367594</t>
+          <t>1460785</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2240313</t>
+          <t>2179048</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2137174</t>
+          <t>2109167</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2481254</t>
+          <t>2238815</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2189370</t>
+          <t>2112822</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2068986</t>
+          <t>2061717</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2478559</t>
+          <t>2166195</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4429683</t>
+          <t>4291870</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4239660</t>
+          <t>4207704</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4776886</t>
+          <t>4373595</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>509078</t>
+          <t>572194</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>406850</t>
+          <t>531130</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>564707</t>
+          <t>620722</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>745588</t>
+          <t>811311</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>595196</t>
+          <t>767104</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>814836</t>
+          <t>849644</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1254666</t>
+          <t>1383505</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1081173</t>
+          <t>1325899</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1353224</t>
+          <t>1441473</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3370233</t>
+          <t>3433578</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3370233</t>
+          <t>3433578</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3370233</t>
+          <t>3433578</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3572590</t>
+          <t>3631796</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3572590</t>
+          <t>3631796</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3572590</t>
+          <t>3631796</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6942823</t>
+          <t>7065373</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6942823</t>
+          <t>7065373</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6942823</t>
+          <t>7065373</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
